--- a/Setting/BCIO-setting-hierarchy.xlsx
+++ b/Setting/BCIO-setting-hierarchy.xlsx
@@ -443,32 +443,32 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>subontology</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>BFO:0000141</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -587,7 +587,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>immaterial entity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -596,16 +596,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ENVO:01000813</t>
+          <t>BFO:0000029</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -614,7 +609,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>astronomical body part</t>
+          <t>site</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -624,14 +619,26 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>A material part of an astronomical body.</t>
+          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>BFO_0000029</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ENVO:00000000</t>
+          <t>BCIO:026041</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -641,7 +648,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>geographic feature</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -650,14 +657,26 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
+          <t>Methods of traveling from one place to another.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>NCIT_C141286</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENVO:00000002</t>
+          <t>BCIO:026043</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -668,7 +687,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>anthropogenic geographic feature</t>
+          <t>private transportation</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -676,14 +695,26 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
+          <t>A form of transportation owned by an individual for individual or group use.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>car; bicycle; motorbike</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENVO:00000562</t>
+          <t>BCIO:026042</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -694,7 +725,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>park</t>
+          <t>public transportation</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -702,26 +733,30 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>ENVO:00000562</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>bus; train; plane</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>NCIT:C141287</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENVO:01001199</t>
+          <t>BCIO:026045</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -729,25 +764,33 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>terrestrial environmental zone</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ambulance</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
+          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENVO:01001305</t>
+          <t>BCIO:026044</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -758,7 +801,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>vegetated area</t>
+          <t>mobile intervention venue</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -766,14 +809,26 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
+          <t>A form of transportation delivering interventions in transient locations.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>mobile van</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENVO:00000106</t>
+          <t>BCIO:026046</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -781,37 +836,33 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>grassland area</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>outdoor environment</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>ENVO:00000106</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>A site which is an outdoor location outside of a building.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENVO:00000109</t>
+          <t>ENVO:00000091</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -820,24 +871,36 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>woodland area</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Land having a cover of trees, shrubs, or both.</t>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>ENVO:00000091</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENVO:00000111</t>
+          <t>BCIO:026048</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -848,7 +911,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>forested area</t>
+          <t>path or pavement</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -856,26 +919,22 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>ENVO:00000111</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>An outdoor environment for the passage of persons or cyclists on land</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENVO:01001784</t>
+          <t>BCIO:026050</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -883,25 +942,33 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>compound astronomical body part</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>path or pavement for cyclists</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
+          <t>A path or pavement for the passage of people using bicycles only on land.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENVO:00000191</t>
+          <t>BCIO:026049</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -910,24 +977,32 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>solid astronomical body part</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>path or pavement for pedestrians</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>A part of an astronomical body which is primarily composed of solid material.</t>
+          <t>A path or pavement for the passage of persons only on land.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENVO:01001886</t>
+          <t>ENVO:00000562</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -936,24 +1011,36 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>landform</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>park</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
+          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ENVO:00000562</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENVO:01001884</t>
+          <t>ENVO:00000106</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -962,24 +1049,36 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>grassland area</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>surface landform</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>A landform which occurs on the surface of an astronomical body.</t>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>ENVO:00000106</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENVO:00000091</t>
+          <t>BCIO:026047</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -990,7 +1089,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>beach</t>
+          <t>water</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -998,47 +1097,60 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>ENVO:00000091</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>An outdoor environment set in an expanse of water.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BFO:0000024</t>
+          <t>ENVO:00000111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>fiat object</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>forest area</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>An area with a high density of trees. A small forest may be called a wood</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>ENVO:00000111</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENVO:01000408</t>
+          <t>ENVO:00000064</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1046,25 +1158,37 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>environmental zone</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
+          <t>An open way for the passage of vehicles, persons, or animals on land</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ENVO:00000064</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENVO:01001813</t>
+          <t>BFO:0000006</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1073,7 +1197,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>spatial region</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1081,16 +1205,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENVO:00000070</t>
+          <t>GAZ:00000448</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1100,7 +1219,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>human construction</t>
+          <t>geographic location</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1109,14 +1228,26 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>A construction that has been assembled by deliberate human effort.</t>
+          <t>A reference to a place on the Earth, by its name or by its geographical location</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GAZ:00000448</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENVO:00000010</t>
+          <t>BCIO:026001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1127,7 +1258,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>transport feature</t>
+          <t>country of intervention</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1135,14 +1266,26 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
+          <t>A geographical location of a country where the intervention takes place.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>United Kingdom; Spain</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENVO:01001272</t>
+          <t>BCIO:026002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1151,62 +1294,62 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>constructed pavement</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>within-country location</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
+          <t>A geographical location within a country.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Region; Town; City; State; New York; Rotterdam</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENVO:00000064</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>road</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>An open way for the passage of vehicles, persons, or animals on land.</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>ENVO:00000064</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OMRSE:00000061</t>
+          <t>ENVO:01000813</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1215,7 +1358,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>architectural structure</t>
+          <t>astronomical body part</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1225,22 +1368,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+          <t>A material part of an astronomical body.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OMRSE:00000062</t>
+          <t>ENVO:00000000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1250,7 +1385,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>geographic feature</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1259,26 +1394,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>An architectural structure that bears some function.</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>OMRSE:00000062</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:026038</t>
+          <t>ENVO:00000002</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1289,7 +1412,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>criminal justice facility</t>
+          <t>anthropogenic geographic feature</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1297,26 +1420,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>prison</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENVO:00000469</t>
+          <t>ENVO:01001784</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1324,41 +1435,25 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>research facility</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>compound astronomical body part</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>ENVO:00000469</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>research lab</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:026036</t>
+          <t>ENVO:00000191</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1369,7 +1464,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>retail facility</t>
+          <t>solid astronomical body part</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1377,26 +1472,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>A facility used as an outlet for shopping.</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>supermarket; market; shopping centre</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>A part of an astronomical body which is primarily composed of solid material.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:026039</t>
+          <t>ENVO:01001886</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1405,32 +1488,24 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>factory facility</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>landform</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:026037</t>
+          <t>ENVO:01001884</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1439,32 +1514,24 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>office facility</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>surface landform</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+          <t>A landform which occurs on the surface of an astronomical body.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OMRSE:00000191</t>
+          <t>ENVO:01001199</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1472,37 +1539,25 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>residential facility</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>terrestrial environmental zone</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>OMRSE:00000191</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:026014</t>
+          <t>ENVO:01001305</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1511,36 +1566,24 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>temporary residence</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>vegetated area</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Hostels; BandB; emergency accomnodation</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
+          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:026013</t>
+          <t>ENVO:00000109</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1552,71 +1595,42 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>homeless setting</t>
+          <t>woodland area</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>A residential facility where an individual is living that is not stable and secure.</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>an architectural structure for which an individual does not have a legal right to stay</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
+          <t>Land having a cover of trees, shrubs, or both.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:026010</t>
+          <t>BFO:0000024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>fiat object</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>multiple occupancy residence</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>bedsit</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:026012</t>
+          <t>ENVO:01000408</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1624,75 +1638,59 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>environmental zone</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>residential care or assisted living</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where multiple vulnerable people live</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>retirement home</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
+          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:026011</t>
+          <t>OMRSE:00000061</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>architectural structure</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>student residence</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where many students live.</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>student hall</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:026009</t>
+          <t>OMRSE:00000062</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1700,33 +1698,37 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>household residence</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An architectural structure that bears some function.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>OMRSE:00000062</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:026022</t>
+          <t>OMRSE:00000191</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1737,7 +1739,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>educational facility</t>
+          <t>residential facility</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -1745,22 +1747,26 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>A facility in which formal education is provided to a student population.</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>OMRSE:00000191</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:026028</t>
+          <t>BCIO:026009</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1772,29 +1778,29 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>university facility</t>
+          <t>household residence</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>An educational facility in which students study for degrees and academic research is done.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:026023</t>
+          <t>BCIO:026013</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1806,33 +1812,33 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>early years facility</t>
+          <t>homeless setting</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>An educational facility in which pre-school education is provided.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A residential facility where an individual is living that is not stable and secure.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>nursery school</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>an architectural structure for which an individual does not have a legal right to stay</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:026027</t>
+          <t>BCIO:026010</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1844,29 +1850,33 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>vocational facility</t>
+          <t>multiple occupancy residence</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>bedsit</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OMRSE:00000064</t>
+          <t>BCIO:026012</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1876,35 +1886,35 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>school facility</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>residential care or assisted living</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>OMRSE:00000064</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+          <t>A multiple occupancy residence where multiple vulnerable people live</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>retirement home</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:026026</t>
+          <t>BCIO:026011</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1917,32 +1927,32 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>secondary school</t>
+          <t>student residence</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A multiple occupancy residence where many students live.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>high school</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>student hall</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:026025</t>
+          <t>BCIO:026014</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1952,31 +1962,35 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>middle school</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>temporary residence</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>A school facility providing education between primary and secondary school.</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hostels; BandB; emergency accomnodation</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:026024</t>
+          <t>BCIO:026022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1985,32 +1999,32 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>educational facility</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>primary school</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>A school facility for younger children, typically aged between five and eleven.</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility in which formal education is provided to a student population.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OMRSE:00000102</t>
+          <t>BCIO:026023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2019,36 +2033,36 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>health care facility</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>early years facility</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>OMRSE:00000102</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+          <t>An educational facility in which pre-school education is provided.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>nursery school</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:026016</t>
+          <t>BCIO:026027</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2060,33 +2074,29 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>doctor-led primary care facility</t>
+          <t>vocational facility</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>A healthcare facility led by doctors.</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>general practitioners surgery; doctor surgery</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:026017</t>
+          <t>OMRSE:00000064</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2098,29 +2108,33 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>care home facility</t>
+          <t>school facility</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>OMRSE:00000064</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:026019</t>
+          <t>BCIO:026025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2130,35 +2144,31 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>community healthcare facility</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>middle school</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>A clinic providing healthcare services to people in a certain area</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A school facility providing education between primary and secondary school.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>polyclinic</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:026020</t>
+          <t>BCIO:026026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2171,28 +2181,32 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>community outpatient clinic facility</t>
+          <t>secondary school</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>high school</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OMRSE:00000104</t>
+          <t>BCIO:026024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2202,35 +2216,31 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>hospice facility</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>primary school</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>OMRSE:00000104</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
+          <t>A school facility for younger children, typically aged between five and eleven.</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OMRSE:00000150</t>
+          <t>BCIO:026028</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2242,21 +2252,29 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>community living health care facility</t>
+          <t>university facility</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
+          <t>An educational facility in which students study for degrees and academic research is done.</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OMRSE:00000106</t>
+          <t>BCIO:026040</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2265,36 +2283,36 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>military facility</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>A facility to assist in physical or addiction recovery</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>OMRSE:00000106</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+          <t>A facility relating to or characteristic of soldiers or armed forces</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>army; navy; air force</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:026018</t>
+          <t>BCIO:026029</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2303,32 +2321,36 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>community facility</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>drug or alcohol rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>food bank; recycling centre</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:026051</t>
+          <t>BCIO:026030</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2340,33 +2362,33 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>psychiatric facility</t>
+          <t>sport and exercise facility</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>NCIT:C53536</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+          <t>A community facility used for exercising.</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>gym; stadium; tennis court; swimming pool</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PDRO:0000074</t>
+          <t>BCIO:026031</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2378,33 +2400,33 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>pharmacy facility</t>
+          <t>social centre or Community Hall facility</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>PDRO:0000074</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+          <t>A community facility used for socialising by those living in a given area.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>YMCA; working mens club</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:026021</t>
+          <t>BCIO:026034</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2416,29 +2438,33 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>dentist facility</t>
+          <t>hospitality and catering facility</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>A healthcare facility where dental healthcare is provided.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A community facility used to serve food.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>diner; restaurant; pub; bar</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OMRSE:00000063</t>
+          <t>BCIO:026033</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2450,33 +2476,33 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>hospital facility</t>
+          <t>religious facility</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>OMRSE:00000063</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>mosque; church; temple</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OMRSE:00000114</t>
+          <t>BCIO:026035</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2486,35 +2512,35 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>emergency department facility</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>arts and entertainment facility</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>OMRSE:00000114</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+          <t>A community facility designed to entertain or amuse.</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>cinema; theatre; disco</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:026015</t>
+          <t>BCIO:026032</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2524,31 +2550,31 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hospital outpatient clinic facility</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>library facility</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A community facility containing a collection of books and learning resources for loan.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:026040</t>
+          <t>BCIO:026039</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2559,7 +2585,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>military facility</t>
+          <t>factory facility</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -2567,26 +2593,22 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>A facility relating to or characteristic of soldiers or armed forces</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>army; navy; air force</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:026029</t>
+          <t>OMRSE:00000102</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2597,7 +2619,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>community facility</t>
+          <t>health care facility</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -2605,26 +2627,26 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>food bank; recycling centre</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>OMRSE:00000102</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:026032</t>
+          <t>BCIO:026019</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2636,29 +2658,33 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>library facility</t>
+          <t>community healthcare facility</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>A community facility containing a collection of books and learning resources for loan.</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A clinic providing healthcare services to people in a certain area</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>polyclinic</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:026033</t>
+          <t>BCIO:026020</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2668,35 +2694,31 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>religious facility</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>community outpatient clinic facility</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>mosque; church; temple</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:026035</t>
+          <t>BCIO:026021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2708,33 +2730,29 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>arts and entertainment facility</t>
+          <t>dentist facility</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>A community facility designed to entertain or amuse.</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A healthcare facility where dental healthcare is provided.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>cinema; theatre; disco</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:026031</t>
+          <t>BCIO:026016</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2746,33 +2764,33 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>social centre or Community Hall facility</t>
+          <t>doctor-led primary care facility</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>A community facility used for socialising by those living in a given area.</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A healthcare facility led by doctors.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>YMCA; working mens club</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>general practitioners surgery; doctor surgery</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:026034</t>
+          <t>OMRSE:00000150</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2784,33 +2802,21 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>hospitality and catering facility</t>
+          <t>community living health care facility</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>A community facility used to serve food.</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>diner; restaurant; pub; bar</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr"/>
+          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:026030</t>
+          <t>OMRSE:00000106</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2820,94 +2826,107 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>sport and exercise facility</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>rehabilitation facility</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>A community facility used for exercising.</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility to assist in physical or addiction recovery</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>gym; stadium; tennis court; swimming pool</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>OMRSE:00000106</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BFO:0000141</t>
+          <t>BCIO:026018</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>immaterial entity</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>drug or alcohol rehabilitation facility</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BFO:0000029</t>
+          <t>PDRO:0000074</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>pharmacy facility</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>BFO_0000029</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
+          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>PDRO:0000074</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:026046</t>
+          <t>OMRSE:00000063</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2915,33 +2934,37 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>outdoor environment</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>hospital facility</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>A site which is an outdoor location outside of a building.</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A health care facility that bears the function to provide acute and intensive healthcare services and that is run by a hospital organization and is the bearer of a hospital function.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>OMRSE:00000063</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:026047</t>
+          <t>OMRSE:00000114</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2950,32 +2973,36 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>emergency department facility</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>An outdoor environment set in an expanse of water.</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>OMRSE:00000114</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:026048</t>
+          <t>BCIO:026015</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2984,32 +3011,32 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>path or pavement</t>
-        </is>
-      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>hospital outpatient clinic facility</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>An outdoor environment for the passage of persons or cyclists on land</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:026050</t>
+          <t>OMRSE:00000104</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3021,29 +3048,33 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>path or pavement for cyclists</t>
+          <t>hospice facility</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>A path or pavement for the passage of people using bicycles only on land.</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>OMRSE:00000104</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:026049</t>
+          <t>BCIO:026017</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3055,29 +3086,29 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>path or pavement for pedestrians</t>
+          <t>care home facility</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>A path or pavement for the passage of persons only on land.</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:026041</t>
+          <t>BCIO:026051</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3085,37 +3116,37 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>psychiatric facility</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Methods of traveling from one place to another.</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>NCIT_C141286</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
+          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>NCIT:C53536</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:026045</t>
+          <t>BCIO:026036</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3126,7 +3157,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ambulance</t>
+          <t>retail facility</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3134,22 +3165,26 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility used as an outlet for shopping.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>supermarket; market; shopping centre</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:026042</t>
+          <t>BCIO:026037</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3160,7 +3195,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>public transportation</t>
+          <t>office facility</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -3168,30 +3203,22 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>NCIT:C141287</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>bus; train; plane</t>
-        </is>
-      </c>
+          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:026044</t>
+          <t>BCIO:026038</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3202,7 +3229,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>mobile intervention venue</t>
+          <t>criminal justice facility</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3210,26 +3237,26 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>A form of transportation delivering interventions in transient locations.</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>mobile van</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>prison</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:026043</t>
+          <t>ENVO:00000469</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3240,7 +3267,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>private transportation</t>
+          <t>research facility</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -3248,26 +3275,30 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>A form of transportation owned by an individual for individual or group use.</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>car; bicycle; motorbike</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>research lab</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>ENVO:00000469</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BFO:0000006</t>
+          <t>ENVO:01001813</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3276,7 +3307,7 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>spatial region</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -3284,11 +3315,16 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GAZ:00000448</t>
+          <t>ENVO:00000070</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3298,7 +3334,7 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>geographic location</t>
+          <t>human construction</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -3307,26 +3343,14 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>A reference to a place on the Earth, by its name or by its geographical location</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>GAZ:00000448</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+          <t>A construction that has been assembled by deliberate human effort.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:026002</t>
+          <t>ENVO:00000010</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3337,7 +3361,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>within-country location</t>
+          <t>transport feature</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -3345,26 +3369,14 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>A geographical location within a country.</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Region; Town; City; State; New York; Rotterdam</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
+          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:026001</t>
+          <t>ENVO:01001272</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3373,31 +3385,19 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>country of intervention</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>constructed pavement</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>A geographical location of a country where the intervention takes place.</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>United Kingdom; Spain</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
+          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3421,7 +3421,7 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
         </is>
       </c>
     </row>
@@ -3450,19 +3450,19 @@
           <t>Features of a given location, such as social and economic characteristics.</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:026007</t>
+          <t>BCIO:026004</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3471,7 +3471,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>population and resource density</t>
+          <t>area social and economic condition</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3481,22 +3481,26 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>disadvantaged area; crime rates; World Bank Classifications</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:026008</t>
+          <t>BCIO:026005</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3506,7 +3510,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>suburban area density</t>
+          <t>low-income area</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -3515,22 +3519,22 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:050915</t>
+          <t>BCIO:026006</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3540,7 +3544,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>rural area density</t>
+          <t>high-income area</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -3549,94 +3553,94 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>developed country</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:050914</t>
+          <t>BCIO:026007</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>urban area density</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>population and resource density</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:026004</t>
+          <t>BCIO:050914</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>area social and economic condition</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>urban area density</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>disadvantaged area; crime rates; World Bank Classifications</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:026005</t>
+          <t>BCIO:050915</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3646,7 +3650,7 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>low-income area</t>
+          <t>rural area density</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -3655,22 +3659,22 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:026006</t>
+          <t>BCIO:026008</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3680,7 +3684,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>high-income area</t>
+          <t>suburban area density</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -3689,21 +3693,17 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>developed country</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Setting/BCIO-setting-hierarchy.xlsx
+++ b/Setting/BCIO-setting-hierarchy.xlsx
@@ -443,32 +443,32 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>informaldefinition</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>comment</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>subontology</t>
         </is>
       </c>
     </row>
@@ -553,14 +553,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>independent continuant</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -572,14 +572,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BFO:0000141</t>
+          <t>BCIO:026003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -587,7 +587,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>immaterial entity</t>
+          <t>attribute of location</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -596,11 +596,24 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Features of a given location, such as social and economic characteristics.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BFO:0000029</t>
+          <t>BCIO:026007</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -609,7 +622,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>population and resource density</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -619,26 +632,22 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>BFO_0000029</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:026041</t>
+          <t>BCIO:026008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -648,7 +657,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>suburban area density</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -657,26 +666,22 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Methods of traveling from one place to another.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>NCIT_C141286</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:026043</t>
+          <t>BCIO:050914</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -684,37 +689,33 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>private transportation</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>urban area density</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>A form of transportation owned by an individual for individual or group use.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>car; bicycle; motorbike</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:026042</t>
+          <t>BCIO:050915</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -722,75 +723,71 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>public transportation</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>rural area density</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>bus; train; plane</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>NCIT:C141287</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:026045</t>
+          <t>BCIO:026004</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>area social and economic condition</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ambulance</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>disadvantaged area; crime rates; World Bank Classifications</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:026044</t>
+          <t>BCIO:026005</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -798,37 +795,33 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>mobile intervention venue</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>low-income area</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>A form of transportation delivering interventions in transient locations.</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>mobile van</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:026046</t>
+          <t>BCIO:026006</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -838,7 +831,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>outdoor environment</t>
+          <t>high-income area</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -847,128 +840,94 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>A site which is an outdoor location outside of a building.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>developed country</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENVO:00000091</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>beach</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>ENVO:00000091</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:026048</t>
+          <t>BFO:0000141</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>immaterial entity</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>path or pavement</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>An outdoor environment for the passage of persons or cyclists on land</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:026050</t>
+          <t>BFO:0000006</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>spatial region</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>path or pavement for cyclists</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>A path or pavement for the passage of people using bicycles only on land.</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:026049</t>
+          <t>GAZ:00000448</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -976,33 +935,37 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>geographic location</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>path or pavement for pedestrians</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>A path or pavement for the passage of persons only on land.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>A reference to a place on the Earth, by its name or by its geographical location.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>GAZ:00000448</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENVO:00000562</t>
+          <t>BCIO:026002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1013,7 +976,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>park</t>
+          <t>within-country location</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1021,26 +984,26 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>ENVO:00000562</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A geographical location within a country.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Region; Town; City; State; New York; Rotterdam</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENVO:00000106</t>
+          <t>BCIO:026001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1051,7 +1014,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>grassland area</t>
+          <t>country of intervention</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1059,60 +1022,64 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>ENVO:00000106</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A geographical location of a country where the intervention takes place.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>United Kingdom; Spain</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:026047</t>
+          <t>BFO:0000029</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>An outdoor environment set in an expanse of water.</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>BFO_0000029</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENVO:00000111</t>
+          <t>BCIO:026046</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1120,32 +1087,28 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>forest area</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>outdoor environment</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>A site which is an outdoor location outside of a building.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>ENVO:00000111</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1172,44 +1135,57 @@
           <t>An open way for the passage of vehicles, persons, or animals on land</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>ENVO:00000064</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>ENVO:00000064</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BFO:0000006</t>
+          <t>BCIO:026047</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>spatial region</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>An outdoor environment set in an expanse of water.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GAZ:00000448</t>
+          <t>ENVO:00000106</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1217,37 +1193,37 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>geographic location</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>grassland area</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>A reference to a place on the Earth, by its name or by its geographical location</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ENVO:00000106</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>GAZ:00000448</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:026001</t>
+          <t>ENVO:00000562</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1258,7 +1234,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>country of intervention</t>
+          <t>park</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1266,26 +1242,26 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>A geographical location of a country where the intervention takes place.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>United Kingdom; Spain</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>ENVO:00000562</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:026002</t>
+          <t>BCIO:026048</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1296,7 +1272,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>within-country location</t>
+          <t>path or pavement</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1304,78 +1280,90 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>A geographical location within a country.</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Region; Town; City; State; New York; Rotterdam</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>An outdoor environment for the passage of persons or cyclists on land</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>BCIO:026049</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>path or pavement for pedestrians</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
-        </is>
-      </c>
+          <t>A path or pavement for the passage of persons only on land.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENVO:01000813</t>
+          <t>BCIO:026050</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>astronomical body part</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>path or pavement for cyclists</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>A material part of an astronomical body.</t>
-        </is>
-      </c>
+          <t>A path or pavement for the passage of people using bicycles only on land.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENVO:00000000</t>
+          <t>ENVO:00000111</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1383,25 +1371,37 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>geographic feature</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>forested area</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
-        </is>
-      </c>
+          <t>An area with a high density of trees. A small forest may be called a wood</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>ENVO:00000111</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENVO:00000002</t>
+          <t>ENVO:00000091</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>anthropogenic geographic feature</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1420,14 +1420,26 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
-        </is>
-      </c>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>ENVO:00000091</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENVO:01001784</t>
+          <t>BCIO:026041</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1437,7 +1449,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>compound astronomical body part</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1446,14 +1458,26 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
-        </is>
-      </c>
+          <t>Methods of traveling from one place to another.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NCIT_C141286</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENVO:00000191</t>
+          <t>BCIO:026043</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1464,7 +1488,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>solid astronomical body part</t>
+          <t>private transportation</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1472,14 +1496,26 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>A part of an astronomical body which is primarily composed of solid material.</t>
+          <t>A form of transportation owned by an individual for individual or group use.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>car; bicycle; motorbike</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENVO:01001886</t>
+          <t>BCIO:026045</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1488,24 +1524,32 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>landform</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ambulance</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
-        </is>
-      </c>
+          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENVO:01001884</t>
+          <t>BCIO:026042</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1514,24 +1558,40 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>public transportation</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>surface landform</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>A landform which occurs on the surface of an astronomical body.</t>
+          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NCIT:C141287</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>bus; train; plane</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENVO:01001199</t>
+          <t>BCIO:026044</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1539,98 +1599,135 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>terrestrial environmental zone</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>mobile intervention venue</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
+          <t>A form of transportation delivering interventions in transient locations.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>mobile van</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENVO:01001305</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>vegetated area</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENVO:00000109</t>
+          <t>OMRSE:00000061</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>architectural structure</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>woodland area</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Land having a cover of trees, shrubs, or both.</t>
-        </is>
-      </c>
+          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BFO:0000024</t>
+          <t>OMRSE:00000062</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>fiat object</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>An architectural structure that bears some function.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>OMRSE:00000062</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENVO:01000408</t>
+          <t>BCIO:026038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1638,59 +1735,75 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>environmental zone</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>criminal justice facility</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
+          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>prison</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OMRSE:00000061</t>
+          <t>OMRSE:00000102</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>architectural structure</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>health care facility</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>OMRSE:00000102</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OMRSE:00000062</t>
+          <t>BCIO:026017</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1698,37 +1811,33 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>facility</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>care home facility</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>An architectural structure that bears some function.</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>OMRSE:00000062</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OMRSE:00000191</t>
+          <t>BCIO:026021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1737,36 +1846,32 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>residential facility</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>dentist facility</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>A healthcare facility where dental healthcare is provided.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>OMRSE:00000191</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:026009</t>
+          <t>OMRSE:00000104</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1778,29 +1883,33 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>household residence</t>
+          <t>hospice facility</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>OMRSE:00000104</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:026013</t>
+          <t>PDRO:0000074</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1812,33 +1921,33 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>homeless setting</t>
+          <t>pharmacy facility</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>A residential facility where an individual is living that is not stable and secure.</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>an architectural structure for which an individual does not have a legal right to stay</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>PDRO:0000074</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:026010</t>
+          <t>BCIO:026016</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1850,33 +1959,33 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>multiple occupancy residence</t>
+          <t>doctor-led primary care facility</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>A healthcare facility led by doctors.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>bedsit</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>general practitioners surgery; doctor surgery</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:026012</t>
+          <t>BCIO:026051</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1886,35 +1995,35 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>residential care or assisted living</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>psychiatric facility</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where multiple vulnerable people live</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>retirement home</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NCIT:C53536</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:026011</t>
+          <t>BCIO:026019</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1924,35 +2033,35 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>student residence</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>community healthcare facility</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where many students live.</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>A clinic providing healthcare services to people in a certain area</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>student hall</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>polyclinic</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:026014</t>
+          <t>BCIO:026020</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1962,35 +2071,31 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>temporary residence</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>community outpatient clinic facility</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Hostels; BandB; emergency accomnodation</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:026022</t>
+          <t>OMRSE:00000063</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1999,32 +2104,36 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>educational facility</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>hospital facility</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>A facility in which formal education is provided to a student population.</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>OMRSE:00000063</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:026023</t>
+          <t>BCIO:026015</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2034,35 +2143,31 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>early years facility</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hospital outpatient clinic facility</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>An educational facility in which pre-school education is provided.</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>nursery school</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:026027</t>
+          <t>OMRSE:00000114</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2072,31 +2177,35 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>vocational facility</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>emergency department facility</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>OMRSE:00000114</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OMRSE:00000064</t>
+          <t>OMRSE:00000150</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2108,33 +2217,21 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>school facility</t>
+          <t>community living health care facility</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>OMRSE:00000064</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:026025</t>
+          <t>OMRSE:00000106</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2147,28 +2244,32 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>middle school</t>
+          <t>rehabilitation facility</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>A school facility providing education between primary and secondary school.</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>A facility to assist in physical or addiction recovery</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>OMRSE:00000106</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:026026</t>
+          <t>BCIO:026018</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2179,34 +2280,30 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>secondary school</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>drug or alcohol rehabilitation facility</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>high school</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:026024</t>
+          <t>BCIO:026040</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2215,32 +2312,36 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>military facility</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>primary school</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>A school facility for younger children, typically aged between five and eleven.</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility relating to or characteristic of soldiers or armed forces</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>army; navy; air force</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:026028</t>
+          <t>BCIO:026037</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2249,32 +2350,32 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>university facility</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>office facility</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>An educational facility in which students study for degrees and academic research is done.</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:026040</t>
+          <t>BCIO:026029</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2285,7 +2386,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>military facility</t>
+          <t>community facility</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2293,26 +2394,26 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>A facility relating to or characteristic of soldiers or armed forces</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>army; navy; air force</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>food bank; recycling centre</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:026029</t>
+          <t>BCIO:026035</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2321,36 +2422,36 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>community facility</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>arts and entertainment facility</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>A community facility designed to entertain or amuse.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>food bank; recycling centre</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>cinema; theatre; disco</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:026030</t>
+          <t>BCIO:026032</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2362,28 +2463,24 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>sport and exercise facility</t>
+          <t>library facility</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>A community facility used for exercising.</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>gym; stadium; tennis court; swimming pool</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A community facility containing a collection of books and learning resources for loan.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2410,16 +2507,16 @@
           <t>A community facility used for socialising by those living in a given area.</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>YMCA; working mens club</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Setting</t>
         </is>
       </c>
     </row>
@@ -2448,23 +2545,23 @@
           <t>A community facility used to serve food.</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>diner; restaurant; pub; bar</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:026033</t>
+          <t>BCIO:026030</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2476,33 +2573,33 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>religious facility</t>
+          <t>sport and exercise facility</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>A community facility used for exercising.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>mosque; church; temple</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>gym; stadium; tennis court; swimming pool</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:026035</t>
+          <t>BCIO:026033</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2514,33 +2611,33 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>arts and entertainment facility</t>
+          <t>religious facility</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>A community facility designed to entertain or amuse.</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>cinema; theatre; disco</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>mosque; church; temple</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:026032</t>
+          <t>BCIO:026022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2549,32 +2646,32 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>library facility</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>educational facility</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>A community facility containing a collection of books and learning resources for loan.</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>A facility in which formal education is provided to a student population.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:026039</t>
+          <t>BCIO:026028</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2583,32 +2680,32 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>factory facility</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>university facility</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>An educational facility in which students study for degrees and academic research is done.</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OMRSE:00000102</t>
+          <t>OMRSE:00000064</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2617,36 +2714,36 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>health care facility</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>school facility</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>OMRSE:00000064</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>OMRSE:00000102</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:026019</t>
+          <t>BCIO:026025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2656,35 +2753,31 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>community healthcare facility</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>middle school</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>A clinic providing healthcare services to people in a certain area</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>polyclinic</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A school facility providing education between primary and secondary school.</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:026020</t>
+          <t>BCIO:026024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2697,28 +2790,28 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>community outpatient clinic facility</t>
+          <t>primary school</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>A school facility for younger children, typically aged between five and eleven.</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:026021</t>
+          <t>BCIO:026026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2728,31 +2821,35 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>dentist facility</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>secondary school</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>A healthcare facility where dental healthcare is provided.</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>high school</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:026016</t>
+          <t>BCIO:026023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2764,33 +2861,33 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>doctor-led primary care facility</t>
+          <t>early years facility</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>A healthcare facility led by doctors.</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>An educational facility in which pre-school education is provided.</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>general practitioners surgery; doctor surgery</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>nursery school</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OMRSE:00000150</t>
+          <t>BCIO:026027</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2802,21 +2899,29 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>community living health care facility</t>
+          <t>vocational facility</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
-        </is>
-      </c>
+          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OMRSE:00000106</t>
+          <t>BCIO:026036</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2825,36 +2930,36 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>retail facility</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>A facility to assist in physical or addiction recovery</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>OMRSE:00000106</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility used as an outlet for shopping.</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>supermarket; market; shopping centre</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:026018</t>
+          <t>BCIO:026039</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2863,32 +2968,32 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>factory facility</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>drug or alcohol rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PDRO:0000074</t>
+          <t>OMRSE:00000191</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2897,36 +3002,36 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>pharmacy facility</t>
-        </is>
-      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>residential facility</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization.</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>OMRSE:00000191</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>PDRO:0000074</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OMRSE:00000063</t>
+          <t>BCIO:026010</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2938,33 +3043,33 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>hospital facility</t>
+          <t>multiple occupancy residence</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>A health care facility that bears the function to provide acute and intensive healthcare services and that is run by a hospital organization and is the bearer of a hospital function.</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>OMRSE:00000063</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>bedsit</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OMRSE:00000114</t>
+          <t>BCIO:026012</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2977,32 +3082,32 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>emergency department facility</t>
+          <t>residential care or assisted living</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>OMRSE:00000114</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A multiple occupancy residence where multiple vulnerable people live</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>retirement home</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:026015</t>
+          <t>BCIO:026011</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3015,28 +3120,32 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>hospital outpatient clinic facility</t>
+          <t>student residence</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A multiple occupancy residence where many students live.</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>student hall</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OMRSE:00000104</t>
+          <t>BCIO:026009</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3048,33 +3157,29 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>hospice facility</t>
+          <t>household residence</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>OMRSE:00000104</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:026017</t>
+          <t>BCIO:026014</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3086,29 +3191,33 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>care home facility</t>
+          <t>temporary residence</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hostels; BandB; emergency accomnodation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:026051</t>
+          <t>BCIO:026013</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3120,33 +3229,33 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>psychiatric facility</t>
+          <t>homeless setting</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>NCIT:C53536</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A residential facility where an individual is living that is not stable and secure.</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>an architectural structure for which an individual does not have a legal right to stay</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:026036</t>
+          <t>ENVO:00000469</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3157,7 +3266,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>retail facility</t>
+          <t>research facility</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3165,60 +3274,51 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>A facility used as an outlet for shopping.</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>ENVO:00000469</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>supermarket; market; shopping centre</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>research lab</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:026037</t>
+          <t>BFO:0000024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>fiat object part</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>office facility</t>
-        </is>
-      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:026038</t>
+          <t>ENVO:01000408</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3226,37 +3326,25 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>criminal justice facility</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>environmental zone</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>prison</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ENVO:00000469</t>
+          <t>ENVO:01001199</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3264,67 +3352,51 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>research facility</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>terrestrial environmental zone</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>research lab</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>ENVO:00000469</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ENVO:01001813</t>
+          <t>ENVO:01001305</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>vegetated area</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
+          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ENVO:00000070</t>
+          <t>ENVO:00000109</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3332,51 +3404,51 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>human construction</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>woodland area</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>A construction that has been assembled by deliberate human effort.</t>
+          <t>Land having a cover of trees, shrubs, or both.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENVO:00000010</t>
+          <t>ENVO:01001813</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>transport feature</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
+          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ENVO:01001272</t>
+          <t>ENVO:00000070</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3384,85 +3456,77 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>human construction</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>constructed pavement</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
+          <t>A construction that has been assembled by deliberate human effort.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>ENVO:00000010</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>specifically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>transport feature</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
+          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:026003</t>
+          <t>ENVO:01001272</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>attribute of location</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>constructed pavement</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Features of a given location, such as social and economic characteristics.</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:026004</t>
+          <t>ENVO:01000813</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3471,7 +3535,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>area social and economic condition</t>
+          <t>astronomical body part</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3481,26 +3545,14 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>disadvantaged area; crime rates; World Bank Classifications</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A material part of an astronomical body.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:026005</t>
+          <t>ENVO:00000000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3510,7 +3562,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>low-income area</t>
+          <t>geographic feature</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -3519,22 +3571,14 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:026006</t>
+          <t>ENVO:00000002</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3542,71 +3586,51 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>high-income area</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>anthropogenic geographic feature</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>developed country</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:026007</t>
+          <t>ENVO:01001784</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>population and resource density</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>compound astronomical body part</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:050914</t>
+          <t>ENVO:00000191</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3614,33 +3638,25 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>urban area density</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>solid astronomical body part</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A part of an astronomical body which is primarily composed of solid material.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:050915</t>
+          <t>ENVO:01001886</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3648,33 +3664,25 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>rural area density</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>landform</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:026008</t>
+          <t>ENVO:01001884</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3682,26 +3690,18 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>suburban area density</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>surface landform</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A landform which occurs on the surface of an astronomical body.</t>
         </is>
       </c>
     </row>

--- a/Setting/BCIO-setting-hierarchy.xlsx
+++ b/Setting/BCIO-setting-hierarchy.xlsx
@@ -443,27 +443,27 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>subontology</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>examples</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -553,14 +553,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t>independent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -572,14 +572,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:026003</t>
+          <t>BFO:0000141</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -587,7 +587,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>attribute of location</t>
+          <t>immaterial entity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -596,24 +596,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Features of a given location, such as social and economic characteristics.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:026007</t>
+          <t>BFO:0000029</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -622,7 +609,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>population and resource density</t>
+          <t>site</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -632,22 +619,26 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>BFO_0000029</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:026008</t>
+          <t>BCIO:026046</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -657,7 +648,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>suburban area density</t>
+          <t>outdoor environment</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -666,22 +657,22 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
+          <t>A site which is an outdoor location outside of a building.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050914</t>
+          <t>BCIO:026047</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -689,33 +680,33 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>urban area density</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
+          <t>An outdoor environment set in an expanse of water.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050915</t>
+          <t>ENVO:00000106</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -723,71 +714,75 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>rural area density</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>grassland area</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ENVO:00000106</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:026004</t>
+          <t>ENVO:00000562</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>area social and economic condition</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>park</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ENVO:00000562</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>disadvantaged area; crime rates; World Bank Classifications</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:026005</t>
+          <t>ENVO:00000111</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -795,33 +790,37 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>low-income area</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>forest area</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+          <t>An area with a high density of trees. A small forest may be called a wood.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ENVO:00000111</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:026006</t>
+          <t>BCIO:026048</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -829,105 +828,139 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>high-income area</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>path or pavement</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
+          <t>An outdoor environment for the passage of persons or cyclists on land</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>developed country</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BCIO:026049</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>independent continuant</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>path or pavement for pedestrians</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
-        </is>
-      </c>
+          <t>A path or pavement for the passage of persons only on land.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BFO:0000141</t>
+          <t>BCIO:026050</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>immaterial entity</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>path or pavement for cyclists</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>A path or pavement for the passage of people using bicycles only on land.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BFO:0000006</t>
+          <t>ENVO:00000064</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>spatial region</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>An open way for the passage of vehicles, persons, or animals on land.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ENVO:00000064</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GAZ:00000448</t>
+          <t>ENVO:00000091</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -935,37 +968,37 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>geographic location</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>A reference to a place on the Earth, by its name or by its geographical location.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>GAZ:00000448</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of wate</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ENVO:00000091</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:026002</t>
+          <t>BCIO:026041</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -973,37 +1006,37 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>within-country location</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>transportation</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>A geographical location within a country.</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>Methods of traveling from one place to another.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NCIT_C141286</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Region; Town; City; State; New York; Rotterdam</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:026001</t>
+          <t>BCIO:026043</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1014,7 +1047,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>country of intervention</t>
+          <t>private transportation</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1022,64 +1055,68 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>A geographical location of a country where the intervention takes place.</t>
+          <t>A form of transportation owned by an individual for individual or group use.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>United Kingdom; Spain</t>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>car; bicycle; motorbike</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BFO:0000029</t>
+          <t>BCIO:026042</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>public transportation</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>BFO_0000029</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>NCIT:C141287</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>bus; train; plane</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:026046</t>
+          <t>BCIO:026044</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1087,33 +1124,37 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>outdoor environment</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>mobile intervention venue</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>A site which is an outdoor location outside of a building.</t>
+          <t>A form of transportation delivering interventions in transient locations.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>mobile van</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENVO:00000064</t>
+          <t>BCIO:026045</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1124,7 +1165,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>ambulance</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1132,60 +1173,43 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>An open way for the passage of vehicles, persons, or animals on land</t>
+          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>ENVO:00000064</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:026047</t>
+          <t>BFO:0000006</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>spatial region</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>An outdoor environment set in an expanse of water.</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENVO:00000106</t>
+          <t>GAZ:00000448</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1193,37 +1217,37 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>grassland area</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>geographic location</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation.</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>ENVO:00000106</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>A reference to a place on the Earth, by its name or by its geographical location.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>GAZ:00000448</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENVO:00000562</t>
+          <t>BCIO:026001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1234,7 +1258,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>park</t>
+          <t>country of intervention</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1242,26 +1266,26 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
+          <t>A geographical location of a country where the intervention takes place.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>ENVO:00000562</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>United Kingdom; Spain</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:026048</t>
+          <t>BCIO:026002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1272,7 +1296,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>path or pavement</t>
+          <t>within-country location</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1280,90 +1304,73 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>An outdoor environment for the passage of persons or cyclists on land</t>
+          <t>A geographical location within a country.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Region; Town; City; State; New York; Rotterdam</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:026049</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>path or pavement for pedestrians</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>A path or pavement for the passage of persons only on land.</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:026050</t>
+          <t>BFO:0000024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>fiat object</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>path or pavement for cyclists</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>A path or pavement for the passage of people using bicycles only on land.</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENVO:00000111</t>
+          <t>ENVO:01000408</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1371,37 +1378,25 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>forested area</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>environmental zone</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>ENVO:00000111</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENVO:00000091</t>
+          <t>ENVO:01001199</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1409,37 +1404,25 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>beach</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>terrestrial environmental zone</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>ENVO:00000091</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:026041</t>
+          <t>ENVO:01001305</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1447,37 +1430,25 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>vegetated area</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Methods of traveling from one place to another.</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>NCIT_C141286</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:026043</t>
+          <t>ENVO:00000109</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1486,70 +1457,50 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>private transportation</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>woodland area</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>A form of transportation owned by an individual for individual or group use.</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>car; bicycle; motorbike</t>
+          <t>Land having a cover of trees, shrubs, or both.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:026045</t>
+          <t>ENVO:01001813</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>ambulance</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:026042</t>
+          <t>ENVO:00000070</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1557,41 +1508,25 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>public transportation</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>human construction</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>NCIT:C141287</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>bus; train; plane</t>
+          <t>A construction that has been assembled by deliberate human effort.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:026044</t>
+          <t>ENVO:00000010</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1602,7 +1537,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>mobile intervention venue</t>
+          <t>transport feature</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1610,52 +1545,40 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>A form of transportation delivering interventions in transient locations.</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>mobile van</t>
+          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>ENVO:01001272</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>constructed pavement</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OMRSE:00000061</t>
+          <t>ENVO:01000813</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1664,7 +1587,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>architectural structure</t>
+          <t>astronomical body part</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1674,22 +1597,14 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+          <t>A material part of an astronomical body.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OMRSE:00000062</t>
+          <t>ENVO:01001784</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1699,7 +1614,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>compound astronomical body part</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1708,26 +1623,14 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>An architectural structure that bears some function.</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>OMRSE:00000062</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
+          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:026038</t>
+          <t>ENVO:00000191</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1738,7 +1641,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>criminal justice facility</t>
+          <t>solid astronomical body part</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -1746,26 +1649,14 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>prison</t>
+          <t>A part of an astronomical body which is primarily composed of solid material.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OMRSE:00000102</t>
+          <t>ENVO:01001886</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1774,36 +1665,24 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>health care facility</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>landform</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>OMRSE:00000102</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
+          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:026017</t>
+          <t>ENVO:01001884</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1813,31 +1692,23 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>care home facility</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>surface landform</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+          <t>A landform which occurs on the surface of an astronomical body.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:026021</t>
+          <t>ENVO:00000000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1845,33 +1716,25 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>geographic feature</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>dentist facility</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>A healthcare facility where dental healthcare is provided.</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OMRSE:00000104</t>
+          <t>ENVO:00000002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1880,74 +1743,58 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>hospice facility</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>anthropogenic geographic feature</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>OMRSE:00000104</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
+          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PDRO:0000074</t>
+          <t>OMRSE:00000061</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>architectural structure</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>pharmacy facility</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization</t>
+          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>PDRO:0000074</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:026016</t>
+          <t>OMRSE:00000062</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1955,37 +1802,37 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>doctor-led primary care facility</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>A healthcare facility led by doctors.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>An architectural structure that bears some function.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>OMRSE:00000062</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>general practitioners surgery; doctor surgery</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:026051</t>
+          <t>OMRSE:00000191</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1994,36 +1841,36 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>psychiatric facility</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>residential facility</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>NCIT:C53536</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
+          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>OMRSE:00000191</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:026019</t>
+          <t>BCIO:026014</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2035,33 +1882,33 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>community healthcare facility</t>
+          <t>temporary residence</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>A clinic providing healthcare services to people in a certain area</t>
+          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>polyclinic</t>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Hostels; BandB; emergency accomnodation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:026020</t>
+          <t>BCIO:026009</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2071,31 +1918,31 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>community outpatient clinic facility</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>household residence</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
+          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OMRSE:00000063</t>
+          <t>BCIO:026010</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2107,33 +1954,33 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>hospital facility</t>
+          <t>multiple occupancy residence</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
+          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>OMRSE:00000063</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>bedsit</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:026015</t>
+          <t>BCIO:026011</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2146,28 +1993,32 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>hospital outpatient clinic facility</t>
+          <t>student residence</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
+          <t>A multiple occupancy residence where many students live.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>student hall</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OMRSE:00000114</t>
+          <t>BCIO:026012</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2180,32 +2031,32 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>emergency department facility</t>
+          <t>residential care or assisted living</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
+          <t>A multiple occupancy residence where multiple vulnerable people live</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>OMRSE:00000114</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>retirement home</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OMRSE:00000150</t>
+          <t>BCIO:026013</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2217,21 +2068,33 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>community living health care facility</t>
+          <t>homeless setting</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
+          <t>A residential facility where an individual is living that is not stable and secure.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>an architectural structure for which an individual does not have a legal right to stay</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OMRSE:00000106</t>
+          <t>BCIO:026022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2240,36 +2103,32 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>educational facility</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>A facility to assist in physical or addiction recovery</t>
+          <t>A facility in which formal education is provided to a student population.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>OMRSE:00000106</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:026018</t>
+          <t>BCIO:026028</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2279,31 +2138,31 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>university facility</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>drug or alcohol rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
+          <t>An educational facility in which students study for degrees and academic research is done.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:026040</t>
+          <t>BCIO:026023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2312,36 +2171,36 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>military facility</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>early years facility</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>A facility relating to or characteristic of soldiers or armed forces</t>
+          <t>An educational facility in which pre-school education is provided.</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>army; navy; air force</t>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>nursery school</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:026037</t>
+          <t>OMRSE:00000064</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2350,32 +2209,36 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>office facility</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>school facility</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+          <t>A facility that is run by a school organization and is the bearer of a school function</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>OMRSE:00000064</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:026029</t>
+          <t>BCIO:026024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2384,36 +2247,32 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>community facility</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>primary school</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
+          <t>A school facility for younger children, typically aged between five and eleven.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>food bank; recycling centre</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:026035</t>
+          <t>BCIO:026025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2423,35 +2282,31 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>arts and entertainment facility</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>middle school</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>A community facility designed to entertain or amuse.</t>
+          <t>A school facility providing education between primary and secondary school.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>cinema; theatre; disco</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:026032</t>
+          <t>BCIO:026026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2461,31 +2316,35 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>library facility</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>secondary school</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>A community facility containing a collection of books and learning resources for loan.</t>
+          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>high school</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:026031</t>
+          <t>BCIO:026027</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2497,33 +2356,29 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>social centre or Community Hall facility</t>
+          <t>vocational facility</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>A community facility used for socialising by those living in a given area.</t>
+          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>YMCA; working mens club</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:026034</t>
+          <t>ENVO:00000469</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2532,36 +2387,40 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>hospitality and catering facility</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>research facility</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>A community facility used to serve food.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
+          <t>A facility which supports the undertaking of scientific research or measurements.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>ENVO:00000469</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>diner; restaurant; pub; bar</t>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>research lab</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:026030</t>
+          <t>BCIO:026036</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2570,36 +2429,36 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>sport and exercise facility</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>retail facility</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>A community facility used for exercising.</t>
+          <t>A facility used as an outlet for shopping.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>gym; stadium; tennis court; swimming pool</t>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>supermarket; market; shopping centre</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:026033</t>
+          <t>BCIO:026039</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2608,36 +2467,32 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>religious facility</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>factory facility</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
+          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>mosque; church; temple</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:026022</t>
+          <t>BCIO:026037</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2648,7 +2503,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>educational facility</t>
+          <t>office facility</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -2656,22 +2511,22 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>A facility in which formal education is provided to a student population.</t>
+          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:026028</t>
+          <t>BCIO:026029</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2680,32 +2535,36 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>university facility</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>community facility</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>An educational facility in which students study for degrees and academic research is done.</t>
+          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>food bank; recycling centre</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OMRSE:00000064</t>
+          <t>BCIO:026032</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2717,33 +2576,29 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>school facility</t>
+          <t>library facility</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
+          <t>A community facility containing a collection of books and learning resources for loan.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>OMRSE:00000064</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:026025</t>
+          <t>BCIO:026030</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2753,31 +2608,35 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>middle school</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>sport and exercise facility</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>A school facility providing education between primary and secondary school.</t>
+          <t>A community facility used for exercising.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>gym; stadium; tennis court; swimming pool</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:026024</t>
+          <t>BCIO:026031</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2787,31 +2646,35 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>primary school</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>social centre or Community Hall facility</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>A school facility for younger children, typically aged between five and eleven.</t>
+          <t>A community facility used for socialising by those living in a given area.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>YMCA; working mens club</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:026026</t>
+          <t>BCIO:026033</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2821,35 +2684,35 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>secondary school</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>religious facility</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
+          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>high school</t>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>mosque; church; temple</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:026023</t>
+          <t>BCIO:026034</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2861,33 +2724,33 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>early years facility</t>
+          <t>hospitality and catering facility</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>An educational facility in which pre-school education is provided.</t>
+          <t>A community facility used to serve food.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>nursery school</t>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>diner; restaurant; pub; bar</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:026027</t>
+          <t>BCIO:026035</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2899,29 +2762,33 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>vocational facility</t>
+          <t>arts and entertainment facility</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
+          <t>A community facility designed to entertain or amuse.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>cinema; theatre; disco</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:026036</t>
+          <t>BCIO:026040</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2932,7 +2799,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>retail facility</t>
+          <t>military facility</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -2940,26 +2807,26 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>A facility used as an outlet for shopping.</t>
+          <t>A facility relating to or characteristic of soldiers or armed forces</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>supermarket; market; shopping centre</t>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>army; navy; air force</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:026039</t>
+          <t>BCIO:026038</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2970,7 +2837,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>factory facility</t>
+          <t>criminal justice facility</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -2978,22 +2845,26 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
+          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>prison</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OMRSE:00000191</t>
+          <t>OMRSE:00000102</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3004,7 +2875,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>residential facility</t>
+          <t>health care facility</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3012,26 +2883,26 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>OMRSE:00000191</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr"/>
+          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>OMRSE:00000102</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:026010</t>
+          <t>OMRSE:00000063</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3043,33 +2914,33 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>multiple occupancy residence</t>
+          <t>hospital facility</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
+          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>OMRSE:00000063</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>bedsit</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:026012</t>
+          <t>OMRSE:00000114</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3082,32 +2953,32 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>residential care or assisted living</t>
+          <t>emergency department facility</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where multiple vulnerable people live</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
+          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>OMRSE:00000114</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>retirement home</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:026011</t>
+          <t>BCIO:026015</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3120,32 +2991,28 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>student residence</t>
+          <t>hospital outpatient clinic facility</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where many students live.</t>
+          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>student hall</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:026009</t>
+          <t>BCIO:026019</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3157,29 +3024,33 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>household residence</t>
+          <t>community healthcare facility</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
+          <t>A clinic providing healthcare services to people in a certain area</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>polyclinic</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:026014</t>
+          <t>BCIO:026020</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3189,35 +3060,31 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>temporary residence</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>community outpatient clinic facility</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
+          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hostels; BandB; emergency accomnodation</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:026013</t>
+          <t>BCIO:026021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3229,33 +3096,29 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>homeless setting</t>
+          <t>dentist facility</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>A residential facility where an individual is living that is not stable and secure.</t>
+          <t>A healthcare facility where dental healthcare is provided.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>an architectural structure for which an individual does not have a legal right to stay</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ENVO:00000469</t>
+          <t>OMRSE:00000150</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3264,61 +3127,62 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>research facility</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>community living health care facility</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>ENVO:00000469</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>research lab</t>
+          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BFO:0000024</t>
+          <t>OMRSE:00000106</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>fiat object part</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>rehabilitation facility</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>A facility to assist in physical or addiction recovery</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>OMRSE:00000106</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENVO:01000408</t>
+          <t>BCIO:026018</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3326,25 +3190,33 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>environmental zone</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>drug or alcohol rehabilitation facility</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
-        </is>
-      </c>
+          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ENVO:01001199</t>
+          <t>BCIO:026017</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3352,25 +3224,33 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>terrestrial environmental zone</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>care home facility</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
-        </is>
-      </c>
+          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ENVO:01001305</t>
+          <t>PDRO:0000074</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3379,24 +3259,36 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>vegetated area</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>pharmacy facility</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
-        </is>
-      </c>
+          <t>Un établissement de santé qui a pour fonction d'entreposer, préparer, distribuer et surveiller l'utilisation des médicaments parmi les patients d'une zone géographique donnée ou suivis dans une organisation de soin donnée.</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>PDRO:0000074</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ENVO:00000109</t>
+          <t>BCIO:026016</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3408,47 +3300,71 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>woodland area</t>
+          <t>doctor-led primary care facility</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Land having a cover of trees, shrubs, or both.</t>
+          <t>A healthcare facility led by doctors.</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>general practitioners surgery; doctor surgery</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENVO:01001813</t>
+          <t>BCIO:026051</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>psychiatric facility</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
-        </is>
-      </c>
+          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>NCIT:C53536</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ENVO:00000070</t>
+          <t>OMRSE:00000104</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3456,77 +3372,97 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>human construction</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>hospice facility</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>A construction that has been assembled by deliberate human effort.</t>
-        </is>
-      </c>
+          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>OMRSE:00000104</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENVO:00000010</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>characteristic</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>transport feature</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
+          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ENVO:01001272</t>
+          <t>BCIO:026003</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>attribute of location</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>constructed pavement</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
-        </is>
-      </c>
+          <t>Features of a given location, such as social and economic characteristics.</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ENVO:01000813</t>
+          <t>BCIO:026004</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3535,7 +3471,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>astronomical body part</t>
+          <t>area social and economic condition</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3545,14 +3481,26 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>A material part of an astronomical body.</t>
+          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>disadvantaged area; crime rates; World Bank Classifications</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ENVO:00000000</t>
+          <t>BCIO:026006</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3562,7 +3510,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>geographic feature</t>
+          <t>high-income area</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -3571,14 +3519,26 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
+          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>developed country</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ENVO:00000002</t>
+          <t>BCIO:026005</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3586,51 +3546,67 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>anthropogenic geographic feature</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>low-income area</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
-        </is>
-      </c>
+          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ENVO:01001784</t>
+          <t>BCIO:026007</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>compound astronomical body part</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>population and resource density</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
-        </is>
-      </c>
+          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ENVO:00000191</t>
+          <t>BCIO:026008</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3638,25 +3614,33 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>solid astronomical body part</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>suburban area density</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>A part of an astronomical body which is primarily composed of solid material.</t>
-        </is>
-      </c>
+          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ENVO:01001886</t>
+          <t>BCIO:050914</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3664,25 +3648,33 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>urban area density</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>landform</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
-        </is>
-      </c>
+          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ENVO:01001884</t>
+          <t>BCIO:050915</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3690,20 +3682,28 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>rural area density</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>surface landform</t>
-        </is>
-      </c>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>A landform which occurs on the surface of an astronomical body.</t>
-        </is>
-      </c>
+          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Setting/BCIO-setting-hierarchy.xlsx
+++ b/Setting/BCIO-setting-hierarchy.xlsx
@@ -443,32 +443,32 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>crossreference</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>synonyms</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>comment</t>
         </is>
       </c>
     </row>
@@ -553,14 +553,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>independent continuant</t>
+          <t>characteristic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -572,14 +572,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BFO:0000141</t>
+          <t>BCIO:026003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -587,7 +587,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>immaterial entity</t>
+          <t>attribute of location</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -596,11 +596,24 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Features of a given location, such as social and economic characteristics.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BFO:0000029</t>
+          <t>BCIO:026007</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -609,7 +622,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>population and resource density</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -619,26 +632,22 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>BFO_0000029</t>
+          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:026046</t>
+          <t>BCIO:026008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -648,7 +657,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>outdoor environment</t>
+          <t>suburban area density</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -657,22 +666,22 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>A site which is an outdoor location outside of a building.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:026047</t>
+          <t>BCIO:050915</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -680,33 +689,33 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>rural area density</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>An outdoor environment set in an expanse of water.</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENVO:00000106</t>
+          <t>BCIO:050914</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -714,75 +723,71 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>grassland area</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>urban area density</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ENVO:00000106</t>
+          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENVO:00000562</t>
+          <t>BCIO:026004</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>area social and economic condition</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>park</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ENVO:00000562</t>
+          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>disadvantaged area; crime rates; World Bank Classifications</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENVO:00000111</t>
+          <t>BCIO:026005</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -790,37 +795,33 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>forest area</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>low-income area</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ENVO:00000111</t>
+          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:026048</t>
+          <t>BCIO:026006</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -828,139 +829,105 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>path or pavement</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>high-income area</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>An outdoor environment for the passage of persons or cyclists on land</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>developed country</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:026049</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>path or pavement for pedestrians</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>A path or pavement for the passage of persons only on land.</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:026050</t>
+          <t>BFO:0000141</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>immaterial entity</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>path or pavement for cyclists</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>A path or pavement for the passage of people using bicycles only on land.</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENVO:00000064</t>
+          <t>BFO:0000006</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>spatial region</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>road</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>An open way for the passage of vehicles, persons, or animals on land.</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ENVO:00000064</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENVO:00000091</t>
+          <t>GAZ:00000448</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -968,37 +935,37 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>beach</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>geographic location</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of wate</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ENVO:00000091</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>A reference to a place on the Earth, by its name or by its geographical location.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>GAZ:00000448</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:026041</t>
+          <t>BCIO:026002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1006,37 +973,37 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>within-country location</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Methods of traveling from one place to another.</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>NCIT_C141286</t>
+          <t>A geographical location within a country.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Region; Town; City; State; New York; Rotterdam</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:026043</t>
+          <t>BCIO:026001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1047,7 +1014,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>private transportation</t>
+          <t>country of intervention</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1055,68 +1022,64 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>A form of transportation owned by an individual for individual or group use.</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>A geographical location of a country where the intervention takes place.</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>United Kingdom; Spain</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>car; bicycle; motorbike</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:026042</t>
+          <t>BFO:0000029</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>public transportation</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>NCIT:C141287</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>BFO_0000029</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>bus; train; plane</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:026044</t>
+          <t>BCIO:026046</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1124,37 +1087,33 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>mobile intervention venue</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>outdoor environment</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>A form of transportation delivering interventions in transient locations.</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>A site which is an outdoor location outside of a building.</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>mobile van</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:026045</t>
+          <t>ENVO:00000091</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1165,7 +1124,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ambulance</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1173,43 +1132,60 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>ENVO:00000091</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BFO:0000006</t>
+          <t>BCIO:026048</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>spatial region</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>path or pavement</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>An outdoor environment for the passage of persons or cyclists on land</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GAZ:00000448</t>
+          <t>BCIO:026049</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1217,37 +1193,33 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>geographic location</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>path or pavement for pedestrians</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>A reference to a place on the Earth, by its name or by its geographical location.</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>GAZ:00000448</t>
+          <t>A path or pavement for the passage of persons only on land.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:026001</t>
+          <t>BCIO:026050</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1256,36 +1228,32 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>country of intervention</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>path or pavement for cyclists</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>A geographical location of a country where the intervention takes place.</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>A path or pavement for the passage of people using bicycles only on land.</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>United Kingdom; Spain</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:026002</t>
+          <t>ENVO:00000106</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1296,7 +1264,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>within-country location</t>
+          <t>grassland area</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1304,73 +1272,102 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>A geographical location within a country.</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>ENVO:00000106</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Region; Town; City; State; New York; Rotterdam</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>ENVO:00000111</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>forested area</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
-        </is>
-      </c>
+          <t>An area with a high density of trees. A small forest may be called a wood.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ENVO:00000111</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BFO:0000024</t>
+          <t>ENVO:00000064</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>fiat object</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>An open way for the passage of vehicles, persons, or animals on land.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>ENVO:00000064</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENVO:01000408</t>
+          <t>ENVO:00000562</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1378,25 +1375,37 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>environmental zone</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>park</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
-        </is>
-      </c>
+          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ENVO:00000562</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENVO:01001199</t>
+          <t>BCIO:026047</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1404,25 +1413,33 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>terrestrial environmental zone</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
-        </is>
-      </c>
+          <t>An outdoor environment set in an expanse of water.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENVO:01001305</t>
+          <t>BCIO:026041</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1430,25 +1447,37 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>vegetated area</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>transportation</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
-        </is>
-      </c>
+          <t>Methods of traveling from one place to another.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>NCIT_C141286</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENVO:00000109</t>
+          <t>BCIO:026045</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1457,50 +1486,74 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>woodland area</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ambulance</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Land having a cover of trees, shrubs, or both.</t>
-        </is>
-      </c>
+          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENVO:01001813</t>
+          <t>BCIO:026042</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>public transportation</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
-        </is>
-      </c>
+          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>NCIT:C141287</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>bus; train; plane</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENVO:00000070</t>
+          <t>BCIO:026043</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1508,25 +1561,37 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>human construction</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>private transportation</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>A construction that has been assembled by deliberate human effort.</t>
-        </is>
-      </c>
+          <t>A form of transportation owned by an individual for individual or group use.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>car; bicycle; motorbike</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENVO:00000010</t>
+          <t>BCIO:026044</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1537,7 +1602,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>transport feature</t>
+          <t>mobile intervention venue</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1545,33 +1610,45 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
-        </is>
-      </c>
+          <t>A form of transportation delivering interventions in transient locations.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>mobile van</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENVO:01001272</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>constructed pavement</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1681,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENVO:01001784</t>
+          <t>ENVO:01001199</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1614,7 +1691,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>compound astronomical body part</t>
+          <t>terrestrial environmental zone</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1623,14 +1700,14 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
+          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENVO:00000191</t>
+          <t>ENVO:01001305</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1641,7 +1718,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>solid astronomical body part</t>
+          <t>vegetated area</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -1649,14 +1726,14 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>A part of an astronomical body which is primarily composed of solid material.</t>
+          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENVO:01001886</t>
+          <t>ENVO:00000109</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1668,21 +1745,21 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>landform</t>
+          <t>woodland area</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
+          <t>Land having a cover of trees, shrubs, or both.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENVO:01001884</t>
+          <t>ENVO:01001784</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1690,25 +1767,25 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>compound astronomical body part</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>surface landform</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>A landform which occurs on the surface of an astronomical body.</t>
+          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENVO:00000000</t>
+          <t>ENVO:00000191</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1716,25 +1793,25 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>geographic feature</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>solid astronomical body part</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
+          <t>A part of an astronomical body which is primarily composed of solid material.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENVO:00000002</t>
+          <t>ENVO:01001886</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1743,58 +1820,50 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>anthropogenic geographic feature</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>landform</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
+          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OMRSE:00000061</t>
+          <t>ENVO:01001884</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>architectural structure</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>surface landform</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+          <t>A landform which occurs on the surface of an astronomical body.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OMRSE:00000062</t>
+          <t>ENVO:00000000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1804,7 +1873,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>geographic feature</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -1813,26 +1882,14 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>An architectural structure that bears some function.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>OMRSE:00000062</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
+          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OMRSE:00000191</t>
+          <t>ENVO:00000002</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1843,7 +1900,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>residential facility</t>
+          <t>anthropogenic geographic feature</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -1851,64 +1908,35 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>OMRSE:00000191</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:026014</t>
+          <t>BFO:0000024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>fiat object</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>temporary residence</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Hostels; BandB; emergency accomnodation</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:026009</t>
+          <t>ENVO:01000408</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1916,71 +1944,51 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>environmental zone</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>household residence</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:026010</t>
+          <t>ENVO:01001813</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>multiple occupancy residence</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>bedsit</t>
+          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:026011</t>
+          <t>ENVO:00000070</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1988,37 +1996,25 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>human construction</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>student residence</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where many students live.</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>student hall</t>
+          <t>A construction that has been assembled by deliberate human effort.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:026012</t>
+          <t>ENVO:00000010</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2027,36 +2023,24 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>transport feature</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>residential care or assisted living</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where multiple vulnerable people live</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>retirement home</t>
+          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:026013</t>
+          <t>ENVO:01001272</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2068,67 +2052,55 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>homeless setting</t>
+          <t>constructed pavement</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>A residential facility where an individual is living that is not stable and secure.</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>an architectural structure for which an individual does not have a legal right to stay</t>
+          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:026022</t>
+          <t>OMRSE:00000061</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>architectural structure</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>educational facility</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>A facility in which formal education is provided to a student population.</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:026028</t>
+          <t>OMRSE:00000062</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2136,33 +2108,37 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>university facility</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>An educational facility in which students study for degrees and academic research is done.</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+          <t>An architectural structure that bears some function.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>OMRSE:00000062</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:026023</t>
+          <t>BCIO:026040</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2171,36 +2147,36 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>early years facility</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>military facility</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>An educational facility in which pre-school education is provided.</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+          <t>A facility relating to or characteristic of soldiers or armed forces</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>army; navy; air force</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>nursery school</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OMRSE:00000064</t>
+          <t>OMRSE:00000191</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2209,36 +2185,36 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>school facility</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>residential facility</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>A facility that is run by a school organization and is the bearer of a school function</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>OMRSE:00000064</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr"/>
+          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>OMRSE:00000191</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:026024</t>
+          <t>BCIO:026014</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2248,31 +2224,35 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>primary school</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>temporary residence</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>A school facility for younger children, typically aged between five and eleven.</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Hostels; BandB; emergency accomnodation</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:026025</t>
+          <t>BCIO:026009</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2282,31 +2262,31 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>middle school</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>household residence</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>A school facility providing education between primary and secondary school.</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:026026</t>
+          <t>BCIO:026010</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2316,35 +2296,35 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>secondary school</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>multiple occupancy residence</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>bedsit</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>high school</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:026027</t>
+          <t>BCIO:026012</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2354,31 +2334,35 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>vocational facility</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>residential care or assisted living</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>A multiple occupancy residence where multiple vulnerable people live</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>retirement home</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENVO:00000469</t>
+          <t>BCIO:026011</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2387,40 +2371,36 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>research facility</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>student residence</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>A facility which supports the undertaking of scientific research or measurements.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>ENVO:00000469</t>
+          <t>A multiple occupancy residence where many students live.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>student hall</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>research lab</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:026036</t>
+          <t>BCIO:026013</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2429,36 +2409,36 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>retail facility</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>homeless setting</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>A facility used as an outlet for shopping.</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>A residential facility where an individual is living that is not stable and secure.</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>an architectural structure for which an individual does not have a legal right to stay</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>supermarket; market; shopping centre</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:026039</t>
+          <t>ENVO:00000469</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2469,7 +2449,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>factory facility</t>
+          <t>research facility</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -2477,22 +2457,30 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr"/>
+          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ENVO:00000469</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>research lab</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:026037</t>
+          <t>BCIO:026029</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2503,7 +2491,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>office facility</t>
+          <t>community facility</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -2511,22 +2499,26 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>food bank; recycling centre</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:026029</t>
+          <t>BCIO:026032</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2535,36 +2527,32 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>community facility</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>library facility</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+          <t>A community facility containing a collection of books and learning resources for loan.</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="O65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>food bank; recycling centre</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:026032</t>
+          <t>BCIO:026033</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2576,24 +2564,28 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>library facility</t>
+          <t>religious facility</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>A community facility containing a collection of books and learning resources for loan.</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>mosque; church; temple</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2620,18 +2612,18 @@
           <t>A community facility used for exercising.</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>gym; stadium; tennis court; swimming pool</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>gym; stadium; tennis court; swimming pool</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2658,23 +2650,23 @@
           <t>A community facility used for socialising by those living in a given area.</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>YMCA; working mens club</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>YMCA; working mens club</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:026033</t>
+          <t>BCIO:026034</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2686,33 +2678,33 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>religious facility</t>
+          <t>hospitality and catering facility</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
+          <t>A community facility used to serve food.</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>diner; restaurant; pub; bar</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>mosque; church; temple</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:026034</t>
+          <t>BCIO:026035</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2724,33 +2716,33 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>hospitality and catering facility</t>
+          <t>arts and entertainment facility</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>A community facility used to serve food.</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>A community facility designed to entertain or amuse.</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>cinema; theatre; disco</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>diner; restaurant; pub; bar</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:026035</t>
+          <t>BCIO:026038</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2759,36 +2751,36 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>arts and entertainment facility</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>criminal justice facility</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>A community facility designed to entertain or amuse.</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>prison</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>cinema; theatre; disco</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:026040</t>
+          <t>BCIO:026037</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2799,7 +2791,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>military facility</t>
+          <t>office facility</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -2807,26 +2799,22 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>A facility relating to or characteristic of soldiers or armed forces</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="O72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>army; navy; air force</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:026038</t>
+          <t>BCIO:026039</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2837,7 +2825,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>criminal justice facility</t>
+          <t>factory facility</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -2845,21 +2833,17 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="O73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>prison</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2886,23 +2870,23 @@
           <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>OMRSE:00000102</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OMRSE:00000063</t>
+          <t>OMRSE:00000150</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2914,33 +2898,21 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>hospital facility</t>
+          <t>community living health care facility</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>OMRSE:00000063</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr"/>
+          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OMRSE:00000114</t>
+          <t>OMRSE:00000106</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2953,32 +2925,32 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>emergency department facility</t>
+          <t>rehabilitation facility</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>OMRSE:00000114</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr"/>
+          <t>A facility to assist in physical or addiction recovery</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>OMRSE:00000106</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:026015</t>
+          <t>BCIO:026018</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2989,30 +2961,30 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>hospital outpatient clinic facility</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>drug or alcohol rehabilitation facility</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
+          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:026019</t>
+          <t>OMRSE:00000104</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3024,33 +2996,33 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>community healthcare facility</t>
+          <t>hospice facility</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>A clinic providing healthcare services to people in a certain area</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>OMRSE:00000104</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>polyclinic</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:026020</t>
+          <t>BCIO:026051</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3060,31 +3032,35 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>community outpatient clinic facility</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>psychiatric facility</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr"/>
+          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>NCIT:C53536</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:026021</t>
+          <t>PDRO:0000074</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3096,29 +3072,33 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>dentist facility</t>
+          <t>pharmacy facility</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>A healthcare facility where dental healthcare is provided.</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr"/>
+          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization.</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>PDRO:0000074</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OMRSE:00000150</t>
+          <t>OMRSE:00000063</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3130,21 +3110,33 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>community living health care facility</t>
+          <t>hospital facility</t>
         </is>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
-        </is>
-      </c>
+          <t>A health care facility that bears the function to provide acute and intensive healthcare services and that is run by a hospital organization and is the bearer of a hospital function.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>OMRSE:00000063</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OMRSE:00000106</t>
+          <t>OMRSE:00000114</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3157,32 +3149,32 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>rehabilitation facility</t>
+          <t>emergency department facility</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>A facility to assist in physical or addiction recovery</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>OMRSE:00000106</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr"/>
+          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>OMRSE:00000114</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:026018</t>
+          <t>BCIO:026015</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3193,30 +3185,30 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>drug or alcohol rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>hospital outpatient clinic facility</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
+          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:026017</t>
+          <t>BCIO:026016</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3228,29 +3220,33 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>care home facility</t>
+          <t>doctor-led primary care facility</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
+          <t>A healthcare facility led by doctors.</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>general practitioners surgery; doctor surgery</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PDRO:0000074</t>
+          <t>BCIO:026019</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3262,33 +3258,33 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>pharmacy facility</t>
+          <t>community healthcare facility</t>
         </is>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Un établissement de santé qui a pour fonction d'entreposer, préparer, distribuer et surveiller l'utilisation des médicaments parmi les patients d'une zone géographique donnée ou suivis dans une organisation de soin donnée.</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>PDRO:0000074</t>
+          <t>A clinic providing healthcare services to people in a certain area</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>polyclinic</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:026016</t>
+          <t>BCIO:026020</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3298,35 +3294,31 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>doctor-led primary care facility</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>community outpatient clinic facility</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>A healthcare facility led by doctors.</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr"/>
+          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="O86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>general practitioners surgery; doctor surgery</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:026051</t>
+          <t>BCIO:026017</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3338,33 +3330,29 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>psychiatric facility</t>
+          <t>care home facility</t>
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>NCIT:C53536</t>
+          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OMRSE:00000104</t>
+          <t>BCIO:026021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3376,131 +3364,135 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>hospice facility</t>
+          <t>dentist facility</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>OMRSE:00000104</t>
+          <t>A healthcare facility where dental healthcare is provided.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BCIO:026022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>characteristic</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>educational facility</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
-        </is>
-      </c>
+          <t>A facility in which formal education is provided to a student population.</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:026003</t>
+          <t>BCIO:026027</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>attribute of location</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>vocational facility</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Features of a given location, such as social and economic characteristics.</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
+          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:026004</t>
+          <t>BCIO:026023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>area social and economic condition</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>early years facility</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
+          <t>An educational facility in which pre-school education is provided.</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Setting</t>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>nursery school</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>disadvantaged area; crime rates; World Bank Classifications</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:026006</t>
+          <t>BCIO:026028</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3508,37 +3500,33 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>high-income area</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>university facility</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
+          <t>An educational facility in which students study for degrees and academic research is done.</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="O92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>developed country</t>
-        </is>
-      </c>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:026005</t>
+          <t>OMRSE:00000064</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3546,67 +3534,75 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>low-income area</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>school facility</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr"/>
+          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>OMRSE:00000064</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:026007</t>
+          <t>BCIO:026026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>population and resource density</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>secondary school</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
+          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>high school</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:026008</t>
+          <t>BCIO:026025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3614,33 +3610,33 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>suburban area density</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>middle school</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
+          <t>A school facility providing education between primary and secondary school.</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:050914</t>
+          <t>BCIO:026024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3648,33 +3644,33 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>urban area density</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>primary school</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr"/>
+          <t>A school facility for younger children, typically aged between five and eleven.</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:050915</t>
+          <t>BCIO:026036</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3682,28 +3678,32 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>rural area density</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>retail facility</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
+          <t>A facility used as an outlet for shopping.</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>supermarket; market; shopping centre</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Setting/BCIO-setting-hierarchy.xlsx
+++ b/Setting/BCIO-setting-hierarchy.xlsx
@@ -448,27 +448,27 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>crossreference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>examples</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
         </is>
       </c>
     </row>
@@ -553,14 +553,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>characteristic</t>
+          <t>independent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -572,14 +572,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:026003</t>
+          <t>BFO:0000141</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -587,7 +587,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>attribute of location</t>
+          <t>immaterial entity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -596,24 +596,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Features of a given location, such as social and economic characteristics.</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:026007</t>
+          <t>BFO:0000006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -622,7 +609,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>population and resource density</t>
+          <t>spatial region</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -630,24 +617,11 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:026008</t>
+          <t>GAZ:00000448</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -657,7 +631,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>suburban area density</t>
+          <t>geographic location</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -666,14 +640,18 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>A reference to a place on the Earth, by its name or by its geographical location.</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>GAZ:00000448</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -681,7 +659,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050915</t>
+          <t>BCIO:026001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -689,33 +667,37 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>rural area density</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>country of intervention</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>A geographical location of a country where the intervention takes place.</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>United Kingdom; Spain</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050914</t>
+          <t>BCIO:026002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -723,33 +705,37 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>urban area density</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>within-country location</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>A geographical location within a country.</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Region; Town; City; State; New York; Rotterdam</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:026004</t>
+          <t>BFO:0000029</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -758,7 +744,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>area social and economic condition</t>
+          <t>site</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -768,18 +754,18 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>disadvantaged area; crime rates; World Bank Classifications</t>
+          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>BFO_0000029</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -787,7 +773,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:026005</t>
+          <t>BCIO:026046</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -797,7 +783,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>low-income area</t>
+          <t>outdoor environment</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -806,22 +792,22 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>A site which is an outdoor location outside of a building.</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:026006</t>
+          <t>ENVO:00000091</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -829,29 +815,29 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>high-income area</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>developed country</t>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>ENVO:00000091</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -859,75 +845,109 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BCIO:026048</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>independent continuant</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>path or pavement</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
-        </is>
-      </c>
+          <t>An outdoor environment for the passage of persons or cyclists on land</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BFO:0000141</t>
+          <t>BCIO:026049</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>immaterial entity</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>path or pavement for pedestrians</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>A path or pavement for the passage of persons only on land.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BFO:0000006</t>
+          <t>BCIO:026050</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>spatial region</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>path or pavement for cyclists</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>A path or pavement for the passage of people using bicycles only on land.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GAZ:00000448</t>
+          <t>BCIO:026047</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -935,37 +955,33 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>geographic location</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>A reference to a place on the Earth, by its name or by its geographical location.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>GAZ:00000448</t>
+          <t>An outdoor environment set in an expanse of water.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:026002</t>
+          <t>ENVO:00000106</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -976,7 +992,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>within-country location</t>
+          <t>grassland area</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -984,18 +1000,18 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>A geographical location within a country.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Region; Town; City; State; New York; Rotterdam</t>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>ENVO:00000106</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -1003,7 +1019,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:026001</t>
+          <t>ENVO:00000064</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1014,7 +1030,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>country of intervention</t>
+          <t>road</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1022,18 +1038,18 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>A geographical location of a country where the intervention takes place.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>United Kingdom; Spain</t>
+          <t>An open way for the passage of vehicles, persons, or animals on land.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>ENVO:00000064</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -1041,37 +1057,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BFO:0000029</t>
+          <t>ENVO:00000562</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>park</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>BFO_0000029</t>
+          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>ENVO:00000562</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -1079,7 +1095,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:026046</t>
+          <t>ENVO:00000111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1087,25 +1103,29 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>outdoor environment</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>forested area</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>A site which is an outdoor location outside of a building.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>An area with a high density of trees. A small forest may be called a wood.</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>ENVO:00000111</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -1113,7 +1133,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENVO:00000091</t>
+          <t>BCIO:026041</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1121,29 +1141,29 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>beach</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>transportation</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>ENVO:00000091</t>
+          <t>Methods of traveling from one place to another.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>NCIT_C141286</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
@@ -1151,7 +1171,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:026048</t>
+          <t>BCIO:026044</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1162,7 +1182,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>path or pavement</t>
+          <t>mobile intervention venue</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1170,22 +1190,26 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>An outdoor environment for the passage of persons or cyclists on land</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>A form of transportation delivering interventions in transient locations.</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>mobile van</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:026049</t>
+          <t>BCIO:026042</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1194,32 +1218,40 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>path or pavement for pedestrians</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>public transportation</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>A path or pavement for the passage of persons only on land.</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
+          <t>NCIT:C141287</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>bus; train; plane</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:026050</t>
+          <t>BCIO:026043</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1228,32 +1260,36 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>path or pavement for cyclists</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>private transportation</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>A path or pavement for the passage of people using bicycles only on land.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>A form of transportation owned by an individual for individual or group use.</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>car; bicycle; motorbike</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENVO:00000106</t>
+          <t>BCIO:026045</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1264,7 +1300,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>grassland area</t>
+          <t>ambulance</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1272,102 +1308,74 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>ENVO:00000106</t>
+          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENVO:00000111</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>forested area</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood.</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>ENVO:00000111</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENVO:00000064</t>
+          <t>ENVO:01000813</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>astronomical body part</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>road</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>An open way for the passage of vehicles, persons, or animals on land.</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>ENVO:00000064</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
+          <t>A material part of an astronomical body.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENVO:00000562</t>
+          <t>ENVO:00000000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1375,37 +1383,25 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>park</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>geographic feature</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>ENVO:00000562</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
+          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:026047</t>
+          <t>ENVO:00000002</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1416,7 +1412,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>anthropogenic geographic feature</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1424,22 +1420,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>An outdoor environment set in an expanse of water.</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
+          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:026041</t>
+          <t>ENVO:01001199</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1449,7 +1437,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>terrestrial environmental zone</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1458,26 +1446,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Methods of traveling from one place to another.</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>NCIT_C141286</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
+          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:026045</t>
+          <t>ENVO:01001305</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1488,7 +1464,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ambulance</t>
+          <t>vegetated area</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1496,22 +1472,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
+          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:026042</t>
+          <t>ENVO:00000109</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1520,40 +1488,24 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>public transportation</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>woodland area</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>NCIT:C141287</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>bus; train; plane</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
+          <t>Land having a cover of trees, shrubs, or both.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:026043</t>
+          <t>ENVO:01001784</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1561,37 +1513,25 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>private transportation</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>compound astronomical body part</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>A form of transportation owned by an individual for individual or group use.</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>car; bicycle; motorbike</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
+          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:026044</t>
+          <t>ENVO:00000191</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1602,7 +1542,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>mobile intervention venue</t>
+          <t>solid astronomical body part</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1610,104 +1550,92 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>A form of transportation delivering interventions in transient locations.</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>mobile van</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+          <t>A part of an astronomical body which is primarily composed of solid material.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>ENVO:01001886</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>landform</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENVO:01000813</t>
+          <t>ENVO:01001884</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>astronomical body part</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>surface landform</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>A material part of an astronomical body.</t>
+          <t>A landform which occurs on the surface of an astronomical body.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENVO:01001199</t>
+          <t>ENVO:01001813</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>terrestrial environmental zone</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>An environmental zone which is bounded by material parts of a land mass or the atmosphere or space adjacent to it.</t>
+          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENVO:01001305</t>
+          <t>ENVO:00000070</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1715,25 +1643,25 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>vegetated area</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>human construction</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>A vegetated area is a geographic feature which has ground cover dominated by plant communities.</t>
+          <t>A construction that has been assembled by deliberate human effort.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENVO:00000109</t>
+          <t>ENVO:00000010</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1742,24 +1670,24 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>woodland area</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>transport feature</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Land having a cover of trees, shrubs, or both.</t>
+          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENVO:01001784</t>
+          <t>ENVO:01001272</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1767,51 +1695,46 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>compound astronomical body part</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>constructed pavement</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>A part of an astronomical body which is composed of a continuous medium bearing liquid, gaseous, and solid material in variable quantities.</t>
+          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENVO:00000191</t>
+          <t>BFO:0000024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>fiat object part</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>solid astronomical body part</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>A part of an astronomical body which is primarily composed of solid material.</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENVO:01001886</t>
+          <t>ENVO:01000408</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1819,51 +1742,59 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>environmental zone</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>landform</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>A solid astronomical body part which has been formed from and is composed primarily of the matter of that astronomical body.</t>
+          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENVO:01001884</t>
+          <t>OMRSE:00000061</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>architectural structure</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>surface landform</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>A landform which occurs on the surface of an astronomical body.</t>
-        </is>
-      </c>
+          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENVO:00000000</t>
+          <t>OMRSE:00000062</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1873,7 +1804,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>geographic feature</t>
+          <t>facility</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -1882,14 +1813,26 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>An astrononmical body part which delimited by physical discontinuities with its surroundings.</t>
-        </is>
-      </c>
+          <t>An architectural structure that bears some function.</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>OMRSE:00000062</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENVO:00000002</t>
+          <t>BCIO:026040</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1900,7 +1843,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>anthropogenic geographic feature</t>
+          <t>military facility</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -1908,35 +1851,64 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>An anthropogenic geographic feature is a geographic feature resulting from the influence of human beings on nature.</t>
+          <t>A facility relating to or characteristic of soldiers or armed forces</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>army; navy; air force</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BFO:0000024</t>
+          <t>OMRSE:00000102</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>fiat object</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>health care facility</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>OMRSE:00000102</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ENVO:01000408</t>
+          <t>OMRSE:00000150</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1944,51 +1916,63 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>environmental zone</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>community living health care facility</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>A site which has its extent determined by the presence or influence of one or more components of an environmental system or the processes occurring therein.</t>
+          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ENVO:01001813</t>
+          <t>OMRSE:00000106</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>rehabilitation facility</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
-        </is>
-      </c>
+          <t>A facility to assist in physical or addiction recovery</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>OMRSE:00000106</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ENVO:00000070</t>
+          <t>BCIO:026018</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1996,25 +1980,33 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>human construction</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>drug or alcohol rehabilitation facility</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>A construction that has been assembled by deliberate human effort.</t>
-        </is>
-      </c>
+          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENVO:00000010</t>
+          <t>OMRSE:00000104</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2023,24 +2015,36 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>transport feature</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>hospice facility</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>A construction which enables the movement of humans, their animals or their vehicles.</t>
-        </is>
-      </c>
+          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>OMRSE:00000104</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENVO:01001272</t>
+          <t>BCIO:026021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2052,47 +2056,59 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>constructed pavement</t>
+          <t>dentist facility</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>A construction which comprises a durable surface layer overlying a solid surface intended to sustain vehicular or foot traffic.</t>
-        </is>
-      </c>
+          <t>A healthcare facility where dental healthcare is provided.</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OMRSE:00000061</t>
+          <t>OMRSE:00000063</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>architectural structure</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>hospital facility</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>A material entity that is a human made strcuture with firm connection between its foundation and the ground.</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>OMRSE:00000063</t>
         </is>
       </c>
       <c r="R53" t="inlineStr"/>
@@ -2100,7 +2116,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OMRSE:00000062</t>
+          <t>OMRSE:00000114</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2108,29 +2124,29 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>facility</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>emergency department facility</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>An architectural structure that bears some function.</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>OMRSE:00000062</t>
+          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>OMRSE:00000114</t>
         </is>
       </c>
       <c r="R54" t="inlineStr"/>
@@ -2138,7 +2154,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:026040</t>
+          <t>BCIO:026015</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2147,36 +2163,32 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>military facility</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hospital outpatient clinic facility</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>A facility relating to or characteristic of soldiers or armed forces</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>army; navy; air force</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OMRSE:00000191</t>
+          <t>BCIO:026051</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2185,28 +2197,28 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>residential facility</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>psychiatric facility</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>OMRSE:00000191</t>
+          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>NCIT:C53536</t>
         </is>
       </c>
       <c r="R56" t="inlineStr"/>
@@ -2214,7 +2226,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:026014</t>
+          <t>BCIO:026017</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2226,33 +2238,29 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>temporary residence</t>
+          <t>care home facility</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Hostels; BandB; emergency accomnodation</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:026009</t>
+          <t>BCIO:026019</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2264,29 +2272,33 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>household residence</t>
+          <t>community healthcare facility</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>A clinic providing healthcare services to people in a certain area</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>polyclinic</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:026010</t>
+          <t>BCIO:026020</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2296,35 +2308,31 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>multiple occupancy residence</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>community outpatient clinic facility</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>bedsit</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:026012</t>
+          <t>PDRO:0000074</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2334,27 +2342,27 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>residential care or assisted living</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>établissement de pharmacologie</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where multiple vulnerable people live</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>retirement home</t>
+          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization.</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>PDRO:0000074</t>
         </is>
       </c>
       <c r="R60" t="inlineStr"/>
@@ -2362,7 +2370,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:026011</t>
+          <t>BCIO:026016</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2372,35 +2380,35 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>student residence</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>doctor-led primary care facility</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where many students live.</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>student hall</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
+          <t>A healthcare facility led by doctors.</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>general practitioners surgery; doctor surgery</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:026013</t>
+          <t>BCIO:026022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2409,36 +2417,32 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>homeless setting</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>educational facility</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>A residential facility where an individual is living that is not stable and secure.</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>an architectural structure for which an individual does not have a legal right to stay</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A facility in which formal education is provided to a student population.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ENVO:00000469</t>
+          <t>BCIO:026028</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2447,40 +2451,32 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>research facility</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>university facility</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>ENVO:00000469</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>research lab</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>An educational facility in which students study for degrees and academic research is done.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:026029</t>
+          <t>BCIO:026027</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2489,36 +2485,32 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>community facility</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>vocational facility</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>food bank; recycling centre</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:026032</t>
+          <t>BCIO:026023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2530,29 +2522,33 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>library facility</t>
+          <t>early years facility</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>A community facility containing a collection of books and learning resources for loan.</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>An educational facility in which pre-school education is provided.</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>nursery school</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:026033</t>
+          <t>OMRSE:00000064</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2564,25 +2560,25 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>religious facility</t>
+          <t>school facility</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>mosque; church; temple</t>
+          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>OMRSE:00000064</t>
         </is>
       </c>
       <c r="R66" t="inlineStr"/>
@@ -2590,7 +2586,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:026030</t>
+          <t>BCIO:026024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2600,35 +2596,31 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>sport and exercise facility</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>primary school</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>A community facility used for exercising.</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>gym; stadium; tennis court; swimming pool</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A school facility for younger children, typically aged between five and eleven.</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:026031</t>
+          <t>BCIO:026025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2638,35 +2630,31 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>social centre or Community Hall facility</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>middle school</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>A community facility used for socialising by those living in a given area.</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>YMCA; working mens club</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A school facility providing education between primary and secondary school.</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:026034</t>
+          <t>BCIO:026026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2676,35 +2664,35 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>hospitality and catering facility</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>secondary school</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>A community facility used to serve food.</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>diner; restaurant; pub; bar</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
+          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>high school</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:026035</t>
+          <t>ENVO:00000469</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2713,36 +2701,40 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>arts and entertainment facility</t>
-        </is>
-      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>research facility</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>A community facility designed to entertain or amuse.</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>cinema; theatre; disco</t>
+          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
+          <t>ENVO:00000469</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>research lab</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:026038</t>
+          <t>BCIO:026029</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2753,7 +2745,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>criminal justice facility</t>
+          <t>community facility</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -2761,26 +2753,26 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>prison</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
+          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>food bank; recycling centre</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:026037</t>
+          <t>BCIO:026031</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2789,32 +2781,36 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>office facility</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>social centre or Community Hall facility</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>A community facility used for socialising by those living in a given area.</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>YMCA; working mens club</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:026039</t>
+          <t>BCIO:026034</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2823,32 +2819,36 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>factory facility</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>hospitality and catering facility</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>A community facility used to serve food.</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>diner; restaurant; pub; bar</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OMRSE:00000102</t>
+          <t>BCIO:026035</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2857,36 +2857,36 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>health care facility</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>arts and entertainment facility</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>OMRSE:00000102</t>
+          <t>A community facility designed to entertain or amuse.</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>cinema; theatre; disco</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OMRSE:00000150</t>
+          <t>BCIO:026033</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2898,21 +2898,33 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>community living health care facility</t>
+          <t>religious facility</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>a health care facility that also bears a residence function and thus one in which the patients are also residents of the facility</t>
+          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>mosque; church; temple</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OMRSE:00000106</t>
+          <t>BCIO:026032</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2922,35 +2934,31 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>library facility</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>A facility to assist in physical or addiction recovery</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>OMRSE:00000106</t>
+          <t>A community facility containing a collection of books and learning resources for loan.</t>
         </is>
       </c>
       <c r="O76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:026018</t>
+          <t>BCIO:026030</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2960,31 +2968,35 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>sport and exercise facility</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>drug or alcohol rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>A community facility used for exercising.</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>gym; stadium; tennis court; swimming pool</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OMRSE:00000104</t>
+          <t>OMRSE:00000191</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2993,28 +3005,28 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>hospice facility</t>
-        </is>
-      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>residential facility</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>OMRSE:00000104</t>
+          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>OMRSE:00000191</t>
         </is>
       </c>
       <c r="R78" t="inlineStr"/>
@@ -3022,7 +3034,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:026051</t>
+          <t>BCIO:026009</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3034,33 +3046,29 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>psychiatric facility</t>
+          <t>household residence</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>NCIT:C53536</t>
+          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PDRO:0000074</t>
+          <t>BCIO:026010</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3072,33 +3080,33 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>pharmacy facility</t>
+          <t>multiple occupancy residence</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization.</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>PDRO:0000074</t>
+          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>bedsit</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OMRSE:00000063</t>
+          <t>BCIO:026012</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3108,35 +3116,35 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>hospital facility</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>residential care or assisted living</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>A health care facility that bears the function to provide acute and intensive healthcare services and that is run by a hospital organization and is the bearer of a hospital function.</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>OMRSE:00000063</t>
+          <t>A multiple occupancy residence where multiple vulnerable people live</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>retirement home</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OMRSE:00000114</t>
+          <t>BCIO:026011</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3149,32 +3157,32 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>emergency department facility</t>
+          <t>student residence</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>OMRSE:00000114</t>
+          <t>A multiple occupancy residence where many students live.</t>
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>student hall</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:026015</t>
+          <t>BCIO:026014</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3184,31 +3192,35 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>hospital outpatient clinic facility</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>temporary residence</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Hostels; BandB; emergency accomnodation</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:026016</t>
+          <t>BCIO:026013</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3220,33 +3232,33 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>doctor-led primary care facility</t>
+          <t>homeless setting</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>A healthcare facility led by doctors.</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>general practitioners surgery; doctor surgery</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
+          <t>A residential facility where an individual is living that is not stable and secure.</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>an architectural structure for which an individual does not have a legal right to stay</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:026019</t>
+          <t>BCIO:026038</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3255,36 +3267,36 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>community healthcare facility</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>criminal justice facility</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>A clinic providing healthcare services to people in a certain area</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>polyclinic</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
+          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>prison</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:026020</t>
+          <t>BCIO:026036</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3293,32 +3305,36 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>retail facility</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>community outpatient clinic facility</t>
-        </is>
-      </c>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>A facility used as an outlet for shopping.</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>supermarket; market; shopping centre</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:026017</t>
+          <t>BCIO:026037</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3327,32 +3343,32 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>care home facility</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>office facility</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:026021</t>
+          <t>BCIO:026039</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3361,138 +3377,130 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>dentist facility</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>factory facility</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>A healthcare facility where dental healthcare is provided.</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:026022</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>specifically dependent continuant</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>educational facility</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>A facility in which formal education is provided to a student population.</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:026027</t>
+          <t>BCIO:026003</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>attribute of location</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>vocational facility</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>Features of a given location, such as social and economic characteristics.</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:026023</t>
+          <t>BCIO:026004</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>area social and economic condition</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>early years facility</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>An educational facility in which pre-school education is provided.</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>nursery school</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
+          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>disadvantaged area; crime rates; World Bank Classifications</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:026028</t>
+          <t>BCIO:026005</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3500,33 +3508,33 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>low-income area</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>university facility</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>An educational facility in which students study for degrees and academic research is done.</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OMRSE:00000064</t>
+          <t>BCIO:026006</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3534,75 +3542,71 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>high-income area</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>school facility</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>OMRSE:00000064</t>
+          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
         </is>
       </c>
       <c r="O93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>developed country</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:026026</t>
+          <t>BCIO:026007</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>population and resource density</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>secondary school</t>
-        </is>
-      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>high school</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:026025</t>
+          <t>BCIO:050914</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3610,33 +3614,33 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>urban area density</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>middle school</t>
-        </is>
-      </c>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>A school facility providing education between primary and secondary school.</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:026024</t>
+          <t>BCIO:050915</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3644,33 +3648,33 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>rural area density</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>primary school</t>
-        </is>
-      </c>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>A school facility for younger children, typically aged between five and eleven.</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:026036</t>
+          <t>BCIO:026008</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3678,31 +3682,27 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>retail facility</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>suburban area density</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>A facility used as an outlet for shopping.</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>supermarket; market; shopping centre</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
+          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
     </row>
   </sheetData>

--- a/Setting/BCIO-setting-hierarchy.xlsx
+++ b/Setting/BCIO-setting-hierarchy.xlsx
@@ -826,7 +826,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of wate</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
+          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood.</t>
+          <t>An area with a high density of trees. A small forest may be called a wood</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>établissement de pharmacologie</t>
+          <t>pharmacy facility</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
+          <t>A facility that is run by a school organization and is the bearer of a school function</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
         </is>
       </c>
     </row>
